--- a/public/samples/crypton-treasury-statements.xlsx
+++ b/public/samples/crypton-treasury-statements.xlsx
@@ -1154,7 +1154,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G4" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="5">
@@ -1522,7 +1522,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G20" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="21">
@@ -1568,7 +1568,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G22" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="23">
@@ -1614,7 +1614,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G24" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="25">
@@ -2051,7 +2051,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G43" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="44">
@@ -2396,7 +2396,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G58" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="59">
@@ -2603,7 +2603,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G67" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="68">
@@ -3040,7 +3040,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G86" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="87">
@@ -3316,7 +3316,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G98" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="99">
@@ -3891,7 +3891,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G123" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="124">
@@ -3937,7 +3937,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G125" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="126">
@@ -4098,7 +4098,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G132" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="133">
@@ -4213,7 +4213,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G137" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="138">
@@ -4535,7 +4535,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G151" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="152">
@@ -4627,7 +4627,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G155" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="156">
@@ -4880,7 +4880,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G166" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="167">
@@ -5018,7 +5018,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G172" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="173">
@@ -5271,7 +5271,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G183" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="184">
@@ -5455,7 +5455,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G191" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="192">
@@ -5524,7 +5524,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G194" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="195">
@@ -5593,7 +5593,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G197" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="198">
@@ -5846,7 +5846,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G208" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="209">
@@ -6076,7 +6076,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G218" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="219">
@@ -6375,7 +6375,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G231" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="232">
@@ -6513,7 +6513,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G237" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="238">
@@ -6605,7 +6605,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G241" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="242">
@@ -6789,7 +6789,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G249" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="250">
@@ -7019,7 +7019,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G259" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="260">
@@ -7088,7 +7088,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G262" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="263">
@@ -7341,7 +7341,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G273" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="274">
@@ -7640,7 +7640,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G286" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="287">
@@ -7939,7 +7939,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G299" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="300">
@@ -8445,7 +8445,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G321" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="322">
@@ -8468,7 +8468,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G322" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="323">
@@ -8882,7 +8882,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G340" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="341">
@@ -9273,7 +9273,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G357" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="358">
@@ -9434,7 +9434,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G364" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="365">
@@ -10078,7 +10078,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G392" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="393">
@@ -10147,7 +10147,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G395" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="396">
@@ -10193,7 +10193,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G397" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="398">
@@ -10262,7 +10262,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G400" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="401">
@@ -10538,7 +10538,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G412" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="413">
@@ -10722,7 +10722,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G420" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="421">
@@ -10883,7 +10883,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G427" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="428">
@@ -11067,7 +11067,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G435" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="436">
@@ -11228,7 +11228,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G442" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="443">
@@ -11343,7 +11343,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G447" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="448">
@@ -11458,7 +11458,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G452" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="453">
@@ -11780,7 +11780,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G466" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="467">
@@ -11941,7 +11941,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G473" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="474">
@@ -12309,7 +12309,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G489" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="490">
@@ -12401,7 +12401,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G493" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="494">
@@ -12447,7 +12447,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G495" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="496">
@@ -12608,7 +12608,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G502" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="503">
@@ -12815,7 +12815,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G511" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="512">
@@ -12861,7 +12861,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G513" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="514">
@@ -13183,7 +13183,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G527" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="528">
@@ -13298,7 +13298,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G532" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="533">
@@ -13367,7 +13367,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G535" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="536">
@@ -13528,7 +13528,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G542" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="543">
@@ -13597,7 +13597,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G545" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="546">
@@ -13804,7 +13804,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G554" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="555">
@@ -13896,7 +13896,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G558" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="559">
@@ -14011,7 +14011,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G563" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="564">
@@ -14264,7 +14264,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G574" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="575">
@@ -14356,7 +14356,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G578" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="579">
@@ -14701,7 +14701,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G593" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="594">
@@ -14931,7 +14931,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G603" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="604">
@@ -15092,7 +15092,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G610" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="611">
@@ -15230,7 +15230,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G616" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="617">
@@ -15253,7 +15253,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G617" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="618">
@@ -15276,7 +15276,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G618" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="619">
@@ -15368,7 +15368,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G622" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="623">
@@ -15621,7 +15621,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G633" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="634">
@@ -15667,7 +15667,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G635" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="636">
@@ -15713,7 +15713,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G637" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="638">
@@ -15805,7 +15805,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G641" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="642">
@@ -15874,7 +15874,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G644" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="645">
@@ -16081,7 +16081,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G653" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="654">
@@ -16288,7 +16288,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G662" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="663">
@@ -16334,7 +16334,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G664" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="665">
@@ -16403,7 +16403,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G667" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="668">
@@ -16702,7 +16702,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G680" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="681">
@@ -16725,7 +16725,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G681" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="682">
@@ -16840,7 +16840,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G686" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="687">
@@ -16978,7 +16978,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G692" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="693">
@@ -17093,7 +17093,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G697" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="698">
@@ -17231,7 +17231,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G703" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="704">
@@ -17599,7 +17599,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G719" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="720">
@@ -17645,7 +17645,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G721" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="722">
@@ -17691,7 +17691,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G723" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="724">
@@ -17737,7 +17737,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G725" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="726">
@@ -17829,7 +17829,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G729" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="730">
@@ -18082,7 +18082,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G740" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="741">
@@ -18220,7 +18220,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G746" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="747">
@@ -18266,7 +18266,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G748" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="749">
@@ -18404,7 +18404,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G754" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="755">
@@ -18519,7 +18519,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G759" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="760">
@@ -18703,7 +18703,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G767" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="768">
@@ -18749,7 +18749,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G769" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="770">
@@ -19094,7 +19094,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G784" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="785">
@@ -19140,7 +19140,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G786" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="787">
@@ -19278,7 +19278,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G792" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="793">
@@ -19508,7 +19508,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G802" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="803">
@@ -19945,7 +19945,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G821" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="822">
@@ -20083,7 +20083,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G827" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="828">
@@ -20428,7 +20428,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G842" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="843">
@@ -20451,7 +20451,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G843" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="844">
@@ -20888,7 +20888,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G862" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="863">
@@ -21095,7 +21095,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G871" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="872">
@@ -21118,7 +21118,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G872" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="873">
@@ -21578,7 +21578,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G892" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="893">
@@ -21762,7 +21762,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G900" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="901">
@@ -21854,7 +21854,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G904" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="905">
@@ -22406,7 +22406,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G928" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="929">
@@ -22475,7 +22475,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G931" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="932">
@@ -23096,7 +23096,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G958" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="959">
@@ -23257,7 +23257,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G965" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="966">
@@ -23349,7 +23349,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G969" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="970">
@@ -23487,7 +23487,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G975" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="976">
@@ -24315,7 +24315,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G1011" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1012">
@@ -24338,7 +24338,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G1012" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1013">
@@ -24361,7 +24361,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G1013" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1014">
@@ -24729,7 +24729,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G1029" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1030">
@@ -24890,7 +24890,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G1036" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1037">
@@ -25074,7 +25074,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G1044" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1045">
@@ -25373,7 +25373,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G1057" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1058">
@@ -25442,7 +25442,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G1060" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1061">
@@ -25580,7 +25580,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G1066" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1067">
@@ -25879,7 +25879,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G1079" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1080">
@@ -26316,7 +26316,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G1098" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1099">
@@ -26707,7 +26707,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G1115" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1116">
@@ -27075,7 +27075,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G1131" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1132">
@@ -27282,7 +27282,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G1140" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1141">
@@ -27328,7 +27328,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G1142" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1143">
@@ -27788,7 +27788,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G1162" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1163">
@@ -27926,7 +27926,7 @@
         <v>USDT-Hot-01</v>
       </c>
       <c r="G1168" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1169">
@@ -28202,7 +28202,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G1180" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1181">
@@ -28271,7 +28271,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G1183" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
     <row r="1184">
@@ -28409,7 +28409,7 @@
         <v>DBS-SGD</v>
       </c>
       <c r="G1189" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1190">
@@ -28501,7 +28501,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G1193" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1194">
@@ -28846,7 +28846,7 @@
         <v>JPM-USD</v>
       </c>
       <c r="G1208" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1209">
@@ -29421,7 +29421,7 @@
         <v>BTC-Hot-01</v>
       </c>
       <c r="G1233" t="str">
-        <v>Human review</v>
+        <v>AI auto</v>
       </c>
     </row>
     <row r="1234">
@@ -29766,7 +29766,7 @@
         <v>ETH-Hot-01</v>
       </c>
       <c r="G1248" t="str">
-        <v>AI auto</v>
+        <v>Human review</v>
       </c>
     </row>
   </sheetData>
